--- a/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
+++ b/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/357609b57e560daa/Desktop/Repositories/Studium/Semester_6/ID_Projekt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malte\OneDrive\Desktop\Repositories\Studium\Semester_6\ID_Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_AD4DB114E441178AC67DF4E0AE96D280683EDF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8CBE7BB-D55E-4E81-922B-C38D3488F9F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042631CE-0BF2-4CC3-89AC-4079A9108865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="2064" windowWidth="14478" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Zeitnachweis</t>
   </si>
@@ -37,6 +37,24 @@
   </si>
   <si>
     <t>3 std</t>
+  </si>
+  <si>
+    <t>3 Std</t>
+  </si>
+  <si>
+    <t>externe Quellen Recherche</t>
+  </si>
+  <si>
+    <t>Präsentationsvorbereitung, Recherche</t>
+  </si>
+  <si>
+    <t>Recherche lesen</t>
+  </si>
+  <si>
+    <t>Daten Zusammenfassen</t>
+  </si>
+  <si>
+    <t>Ideen diskutieren, weitere Recherche</t>
   </si>
 </sst>
 </file>
@@ -354,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="26.83984375" customWidth="1"/>
@@ -387,6 +405,72 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>31.03</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>6.04</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>15.04</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>22.04</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>30.04</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
+++ b/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malte\OneDrive\Desktop\Repositories\Studium\Semester_6\ID_Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042631CE-0BF2-4CC3-89AC-4079A9108865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C752A415-D37D-42EF-AB85-8423C76CAF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Zeitnachweis</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>Ideen diskutieren, weitere Recherche</t>
+  </si>
+  <si>
+    <t>2Std</t>
+  </si>
+  <si>
+    <t>externe Quellen Recherche; PPT</t>
+  </si>
+  <si>
+    <t>4Std</t>
   </si>
 </sst>
 </file>
@@ -372,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="26.83984375" customWidth="1"/>
@@ -471,6 +480,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>5.05</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>6.05</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
+++ b/Semester_6/ID_Projekt/Zeitnachweis_ID_Projekt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malte\OneDrive\Desktop\Repositories\Studium\Semester_6\ID_Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C752A415-D37D-42EF-AB85-8423C76CAF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE28279-CEE2-40DB-85B7-DC5872FD8296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Zeitnachweis</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>4Std</t>
+  </si>
+  <si>
+    <t>4std</t>
+  </si>
+  <si>
+    <t>PPT</t>
   </si>
 </sst>
 </file>
@@ -381,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="26.83984375" customWidth="1"/>
@@ -488,7 +494,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -500,6 +506,17 @@
       </c>
       <c r="C11" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>7.05</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
